--- a/sampleprojects/CorporateTax/excel/states/LA_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/LA_corp.xlsx
@@ -70,7 +70,7 @@
     <t>Meets economic nexus threshold ($100K gross receipts, no transaction count as of 2023); result.la_gross_receipts is greater than or equal to result.la_economic_nexus_threshold</t>
   </si>
   <si>
-    <t>result.la_gross_receipts &gt;= result.la_economic_nexus_threshold</t>
+    <t>la_result.gross_receipts &gt;= la_result.economic_nexus_threshold</t>
   </si>
   <si>
     <t>-</t>
@@ -85,7 +85,7 @@
     <t>Physical nexus - filing required</t>
   </si>
   <si>
-    <t>set result.la_has_nexus = true;</t>
+    <t>set la_result.has_nexus = true;</t>
   </si>
   <si>
     <t>X</t>
@@ -97,7 +97,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set result.la_has_nexus = false; set result.la_tax_liability = 0.0;</t>
+    <t>set la_result.has_nexus = false; set la_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate LA Income Adjustments</t>
@@ -115,19 +115,19 @@
     <t>Has Louisiana nexus</t>
   </si>
   <si>
-    <t>result.la_has_nexus is equal to true</t>
+    <t>la_result.has_nexus is equal to true</t>
   </si>
   <si>
     <t>Calculate Louisiana state additions and subtractions; Calculate state-specific income adjustments</t>
   </si>
   <si>
-    <t>set result.la_state_additions = 0.0; if result.la_us_interest_income != 0.0 then set result.la_state_additions = result.la_state_additions + result.la_us_interest_income; endif set result.la_state_subtractions = 0.0; set result.la_state_subtractions = result.la_standard_deduction; if result.la_municipal_interest != 0.0 then set result.la_state_subtractions = result.la_state_subtractions + result.la_municipal_interest; endif add (("Louisiana additions: $" + string value of (result.la_state_additions)) + ", subtractions: $") + string value of (result.la_state_subtractions) to job.audit_trail; add ("Louisiana standard deduction: $" + string value of (result.la_standard_deduction)) + " (new for 2025)" to job.audit_trail;</t>
+    <t>set la_result.state_additions = 0.0; if la_result.us_interest_income != 0.0 then set la_result.state_additions = la_result.state_additions + la_result.us_interest_income; endif set la_result.state_subtractions = 0.0; set la_result.state_subtractions = la_result.standard_deduction; if la_result.municipal_interest != 0.0 then set la_result.state_subtractions = la_result.state_subtractions + la_result.municipal_interest; endif add (("Louisiana additions: $" + string value of (la_result.state_additions)) + ", subtractions: $") + string value of (la_result.state_subtractions) to job.audit_trail; add ("Louisiana standard deduction: $" + string value of (la_result.standard_deduction)) + " (new for 2025)" to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no adjustments</t>
   </si>
   <si>
-    <t>set result.la_state_additions = 0.0; set result.la_state_subtractions = 0.0;</t>
+    <t>set la_result.state_additions = 0.0; set la_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate LA State Tax</t>
@@ -145,19 +145,19 @@
     <t>Has positive taxable income; result.la_apportioned_income is greater than 0</t>
   </si>
   <si>
-    <t>result.la_apportioned_income &gt; 0.0</t>
+    <t>la_result.apportioned_income &gt; 0.0</t>
   </si>
   <si>
     <t>Calculate Louisiana corporate tax (flat rate 5.5% - NEW for 2025); Apply Louisiana 5.5% flat rate</t>
   </si>
   <si>
-    <t>set result.la_taxable_income = the maximum of (result.la_apportioned_income + result.la_state_additions - result.la_state_subtractions) and (0.0); set result.la_tax_liability = the maximum of (result.la_taxable_income * result.la_corp_tax_rate - result.la_state_credits) and (0.0); set result.la_refund_or_owed = result.la_estimated_payments - result.la_tax_liability; add "Louisiana taxable income: $" + string value of (result.la_taxable_income) to job.audit_trail; add "Louisiana tax liability (5.5% flat rate, effective 2025): $" + string value of (result.la_tax_liability) to job.audit_trail;</t>
+    <t>set la_result.taxable_income = the maximum of (la_result.apportioned_income + la_result.state_additions - la_result.state_subtractions) and (0.0); set la_result.tax_liability = the maximum of (la_result.taxable_income * la_result.corp_tax_rate - la_result.state_credits) and (0.0); set la_result.refund_or_owed = la_result.estimated_payments - la_result.tax_liability; add "Louisiana taxable income: $" + string value of (la_result.taxable_income) to job.audit_trail; add "Louisiana tax liability (5.5% flat rate, effective 2025): $" + string value of (la_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>No taxable income - no tax liability</t>
   </si>
   <si>
-    <t>set result.la_taxable_income = 0.0; set result.la_tax_liability = 0.0;</t>
+    <t>set la_result.taxable_income = 0.0; set la_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
@@ -205,13 +205,13 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>result</t>
+    <t>la_result</t>
   </si>
   <si>
     <t>(17 attributes)</t>
   </si>
   <si>
-    <t>la_apportioned_income</t>
+    <t>apportioned_income</t>
   </si>
   <si>
     <t>double</t>
@@ -226,7 +226,7 @@
     <t>Declared from decision-table usage; referenced by LA but never declared (campaign #948 Phase 1)</t>
   </si>
   <si>
-    <t>la_apportionment_formula</t>
+    <t>apportionment_formula</t>
   </si>
   <si>
     <t>string</t>
@@ -238,7 +238,7 @@
     <t>LA uses single-sales factor apportionment (100% sales)</t>
   </si>
   <si>
-    <t>la_corp_tax_rate</t>
+    <t>corp_tax_rate</t>
   </si>
   <si>
     <t>0.055</t>
@@ -247,7 +247,7 @@
     <t>LA corporate income tax rate: 5.5% flat rate (effective 2025, replaced graduated rates up to 7.5%, LA R.S. 47:287)</t>
   </si>
   <si>
-    <t>la_economic_nexus_threshold</t>
+    <t>economic_nexus_threshold</t>
   </si>
   <si>
     <t>100000.0</t>
@@ -256,13 +256,13 @@
     <t>LA economic nexus gross receipts threshold: $100,000</t>
   </si>
   <si>
-    <t>la_estimated_payments</t>
-  </si>
-  <si>
-    <t>la_gross_receipts</t>
-  </si>
-  <si>
-    <t>la_has_nexus</t>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
+  </si>
+  <si>
+    <t>has_nexus</t>
   </si>
   <si>
     <t>boolean</t>
@@ -274,13 +274,13 @@
     <t>Whether corporation has nexus with Louisiana</t>
   </si>
   <si>
-    <t>la_municipal_interest</t>
-  </si>
-  <si>
-    <t>la_refund_or_owed</t>
-  </si>
-  <si>
-    <t>la_standard_deduction</t>
+    <t>municipal_interest</t>
+  </si>
+  <si>
+    <t>refund_or_owed</t>
+  </si>
+  <si>
+    <t>standard_deduction</t>
   </si>
   <si>
     <t>20000.0</t>
@@ -289,37 +289,37 @@
     <t>LA corporate standard deduction: $20,000 (new for 2025 tax reform)</t>
   </si>
   <si>
-    <t>la_state_additions</t>
+    <t>state_additions</t>
   </si>
   <si>
     <t>LA additions to federal taxable income (federal bond interest, certain state tax refunds, etc.)</t>
   </si>
   <si>
-    <t>la_state_credits</t>
+    <t>state_credits</t>
   </si>
   <si>
     <t>LA tax credits (reduced significantly in 2025 reform - many credits eliminated)</t>
   </si>
   <si>
-    <t>la_state_subtractions</t>
+    <t>state_subtractions</t>
   </si>
   <si>
     <t>LA subtractions from federal taxable income (standard deduction, LA municipal interest, qualified property expensing, etc.)</t>
   </si>
   <si>
-    <t>la_tax_liability</t>
+    <t>tax_liability</t>
   </si>
   <si>
     <t>LA corporate income tax liability</t>
   </si>
   <si>
-    <t>la_taxable_income</t>
+    <t>taxable_income</t>
   </si>
   <si>
     <t>LA taxable income after apportionment and modifications</t>
   </si>
   <si>
-    <t>la_transaction_threshold</t>
+    <t>transaction_threshold</t>
   </si>
   <si>
     <t>integer</t>
@@ -331,7 +331,7 @@
     <t>LA eliminated transaction count threshold in 2023</t>
   </si>
   <si>
-    <t>la_us_interest_income</t>
+    <t>us_interest_income</t>
   </si>
 </sst>
 </file>
